--- a/branches/dev/observations-summary.xlsx
+++ b/branches/dev/observations-summary.xlsx
@@ -602,10 +602,10 @@
     <t>MII PR Onkologie Tumormarker</t>
   </si>
   <si>
-    <t>LOINC#26436-6, Observation Category Codes#laboratory</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-tumormarker-loinc (extensible)</t>
+    <t>null#null</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, Rangeĵ, Ratioĵ</t>
@@ -3641,13 +3641,13 @@
         <v>195</v>
       </c>
       <c r="C83" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>13</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>197</v>
